--- a/runs/legacy/season_plan_spond_games.xlsx
+++ b/runs/legacy/season_plan_spond_games.xlsx
@@ -75,10 +75,10 @@
     <sheet name="06.12 U9 Bugården ishall" sheetId="66" state="visible" r:id="rId66"/>
     <sheet name="06.12 U8 Tonsberghallen" sheetId="67" state="visible" r:id="rId67"/>
     <sheet name="12.12 U8 Baerum ishall" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="12.12 JU12 Skien ishall" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="12.12 U12 Baerum ishall" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="12.12 JU10 Schjongshallen" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="12.12 U11 Schjongshallen" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="12.12 U12 Baerum ishall" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="12.12 JU10 Schjongshallen" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="12.12 U11 Schjongshallen" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="13.12 JU12 Skien ishall" sheetId="72" state="visible" r:id="rId72"/>
     <sheet name="13.12 U9 Baerum ishall" sheetId="73" state="visible" r:id="rId73"/>
     <sheet name="13.12 U10 Schjongshallen" sheetId="74" state="visible" r:id="rId74"/>
     <sheet name="13.12 U12 Tonsberghallen" sheetId="75" state="visible" r:id="rId75"/>
@@ -45471,36 +45471,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — JU12 — Skien ishall</t>
+          <t>12.12.2026 (lørdag) — U12 — Baerum ishall</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vertsklubb: Skien</t>
+          <t>Vertsklubb: Jutul</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
+          <t>Deltakende lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:40 • Slutt: 15:20</t>
+          <t>Start: 14:30 • Slutt: 16:10</t>
         </is>
       </c>
     </row>
@@ -45532,12 +45532,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -45550,12 +45550,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -45568,12 +45568,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -45586,12 +45586,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -45604,12 +45604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -45622,12 +45622,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -46077,40 +46077,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — U12 — Baerum ishall</t>
+          <t>12.12.2026 (lørdag) — JU10 — Schjongshallen</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vertsklubb: Jutul</t>
+          <t>Vertsklubb: Ringerike</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
+          <t>Deltakende lag: Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:30 • Slutt: 16:10</t>
+          <t>Start: 10:00 • Slutt: 12:20</t>
         </is>
       </c>
     </row>
@@ -46142,12 +46142,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Jar Rød</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -46160,12 +46160,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -46178,12 +46178,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -46219,7 +46219,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -46232,7 +46232,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -46242,6 +46242,153 @@
       </c>
       <c r="D12" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Frisk Asker Orange</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Frisk Asker Orange</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -46260,15 +46407,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — JU10 — Schjongshallen</t>
+          <t>12.12.2026 (lørdag) — U11 — Schjongshallen</t>
         </is>
       </c>
     </row>
@@ -46282,14 +46429,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
+          <t>Deltakende lag: Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 10:00 • Slutt: 12:20</t>
+          <t>Start: 12:45 • Slutt: 14:45</t>
         </is>
       </c>
     </row>
@@ -46321,12 +46468,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -46339,12 +46486,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -46353,20 +46500,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -46375,66 +46522,66 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -46443,16 +46590,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -46461,98 +46608,110 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
-        </is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
-        </is>
+          <t>Jar Gul</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
-        </is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
-        </is>
+          <t>Jar Gul</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -46561,13 +46720,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
-        </is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -46582,40 +46744,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — U11 — Schjongshallen</t>
+          <t>13.12.2026 (søndag) — JU12 — Skien ishall</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vertsklubb: Ringerike</t>
+          <t>Vertsklubb: Skien</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
+          <t>Deltakende lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:45 • Slutt: 14:45</t>
+          <t>Start: 13:15 • Slutt: 15:00</t>
         </is>
       </c>
     </row>
@@ -46647,12 +46809,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -46665,12 +46827,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ringerike Gul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -46679,20 +46841,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -46701,214 +46863,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ringerike Gul</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Jar Gul</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ringerike Gul</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ringerike Gul</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Jar Gul</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Ringerike Gul</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Jar Gul</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/runs/legacy/season_plan_spond_games.xlsx
+++ b/runs/legacy/season_plan_spond_games.xlsx
@@ -4765,7 +4765,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:50</t>
+          <t>Start: 11:30 • Slutt: 13:50</t>
         </is>
       </c>
     </row>
@@ -30023,7 +30023,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:00 • Slutt: 15:00</t>
+          <t>Start: 14:00 • Slutt: 15:50</t>
         </is>
       </c>
     </row>
@@ -33144,7 +33144,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 14:00</t>
+          <t>Start: 12:00 • Slutt: 13:50</t>
         </is>
       </c>
     </row>

--- a/runs/legacy/season_plan_spond_games.xlsx
+++ b/runs/legacy/season_plan_spond_games.xlsx
@@ -25952,7 +25952,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 11:00 • Slutt: 13:35</t>
+          <t>Start: 10:30 • Slutt: 13:00</t>
         </is>
       </c>
     </row>
